--- a/convergence_analysis.xlsx
+++ b/convergence_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,84 +460,101 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>0.291</v>
+        <v>0.2972</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01905338268755408</v>
+        <v>0.01830863122959934</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004542235132619182</v>
+        <v>0.004570253384660417</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00234704201057069</v>
+        <v>0.0002954283366672236</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="B3" t="n">
-        <v>0.29485</v>
+        <v>0.2958</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01874381540268786</v>
+        <v>0.01877587581617062</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003224232292344954</v>
+        <v>0.002041089708954508</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002479304696514805</v>
+        <v>0.0001525187905435765</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="B4" t="n">
-        <v>0.29712</v>
+        <v>0.29438</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01888128910389329</v>
+        <v>0.01872367803438827</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00204372065410124</v>
+        <v>0.001441250899739528</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002845169240560026</v>
+        <v>9.408187761121804e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="B5" t="n">
-        <v>0.29148</v>
+        <v>0.294585</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01876617796335744</v>
+        <v>0.01867512092000313</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001437078319368851</v>
+        <v>0.001019324967257744</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002685723350039734</v>
+        <v>7.13758975176113e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10000000</v>
+        <v>500000</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2927278</v>
+        <v>0.293736</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01874095421884006</v>
+        <v>0.01873882828500924</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001438882327041235</v>
+        <v>0.0006441353309732358</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002292074558637175</v>
+        <v>4.196111960284056e-05</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.292919</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.01874456925257229</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.000455101592437337</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.079097666439472e-05</v>
       </c>
     </row>
   </sheetData>
